--- a/output/pdf_financials_xlsx/MXG.xlsx
+++ b/output/pdf_financials_xlsx/MXG.xlsx
@@ -965,19 +965,19 @@
         <v>0</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0</v>
+        <v>33.622</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0</v>
+        <v>82.902</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0</v>
+        <v>64.15300000000001</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0</v>
+        <v>84.447</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0</v>
+        <v>85.869</v>
       </c>
     </row>
     <row r="11">
@@ -1049,19 +1049,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.436</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.054</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.016</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.057</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -2059,19 +2059,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>28.019</v>
+        <v>28.455</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>4.834</v>
+        <v>4.888</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>2.203</v>
+        <v>2.219</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>18.83</v>
+        <v>18.887</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>5.707</v>
+        <v>5.757</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>12.677</v>
@@ -2175,19 +2175,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>44.804</v>
+        <v>45.24</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>26.503</v>
+        <v>26.557</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>24.899</v>
+        <v>24.915</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>40.528</v>
+        <v>40.585</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>24.597</v>
+        <v>24.647</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>32.024</v>
@@ -2243,13 +2243,13 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>16.46225760170315</v>
+        <v>16.47283618404089</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>25.12834503112522</v>
+        <v>25.16368641650752</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>15.71382026563428</v>
+        <v>15.74576282014425</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>18.43213997927938</v>
@@ -56220,7 +56220,7 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
@@ -60604,7 +60604,7 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
@@ -73134,7 +73134,7 @@
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
@@ -73637,7 +73637,7 @@
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
@@ -74942,7 +74942,7 @@
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
@@ -75346,7 +75346,7 @@
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
@@ -76342,7 +76342,7 @@
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
@@ -78340,7 +78340,7 @@
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E707" s="5" t="n">

--- a/output/pdf_financials_xlsx/MXG.xlsx
+++ b/output/pdf_financials_xlsx/MXG.xlsx
@@ -1366,7 +1366,7 @@
         <v>-26.344</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>48.714</v>
+        <v>48.718</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>15.246</v>
@@ -1782,7 +1782,7 @@
         <v>-53.689</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>18.476</v>
+        <v>18.48</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>4.377</v>
@@ -2326,7 +2326,7 @@
         <v>-96.33936734320717</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-161.1019247304716</v>
+        <v>-161.1151531185925</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>-140.2704940656914</v>
@@ -2388,7 +2388,7 @@
         <v>-828.0228254164097</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>912.8458498023715</v>
+        <v>913.0434782608695</v>
       </c>
       <c r="L32" s="3" t="n">
         <v>22.16876012965964</v>
@@ -64709,11 +64709,7 @@
           <t>Shareholders</t>
         </is>
       </c>
-      <c r="D570" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+      <c r="D570" t="inlineStr"/>
       <c r="E570" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MXG.xlsx
+++ b/output/pdf_financials_xlsx/MXG.xlsx
@@ -1601,11 +1601,15 @@
       <c r="H20" s="3" t="n">
         <v>-8.981</v>
       </c>
-      <c r="I20" s="3" t="n">
-        <v>-77.309</v>
-      </c>
-      <c r="J20" s="3" t="n">
-        <v>-53.689</v>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K20" s="3" t="n">
         <v>-30.725</v>
@@ -1660,13 +1664,13 @@
         <v>0</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0</v>
+        <v>-81.822</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0</v>
+        <v>-29.874</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0</v>
+        <v>-30.725</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>0</v>
@@ -2787,19 +2791,19 @@
         <v>0</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>2.958</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>4.844</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>4.233</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>1.499</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>1.236</v>
       </c>
       <c r="J40" s="3" t="n">
         <v>0</v>
@@ -2814,13 +2818,13 @@
         <v>0</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>0.031</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="Q40" s="3" t="n">
         <v>0</v>
@@ -2845,19 +2849,19 @@
         <v>30.5</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>29.425</v>
+        <v>32.383</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>38.54</v>
+        <v>43.384</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>28.15</v>
+        <v>32.383</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>20.269</v>
+        <v>21.768</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>20.871</v>
+        <v>22.107</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>1.856</v>
@@ -2872,13 +2876,13 @@
         <v>4.064</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>20.766</v>
+        <v>20.797</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>15.109</v>
+        <v>15.132</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>47.877</v>
+        <v>47.922</v>
       </c>
       <c r="Q41" s="3" t="n">
         <v>6.244</v>
@@ -3251,19 +3255,19 @@
         <v>2.142</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>15.404</v>
+        <v>12.446</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.594</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>7.144</v>
+        <v>2.911</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>3.082</v>
+        <v>1.583</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>3.602</v>
+        <v>2.366</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>121.988</v>
@@ -3278,13 +3282,13 @@
         <v>1.03</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.55</v>
+        <v>1.519</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>4.129</v>
+        <v>4.106</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>12.188</v>
+        <v>12.143</v>
       </c>
       <c r="Q48" s="3" t="n">
         <v>5.161</v>
@@ -4395,46 +4399,46 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>14.527</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>15.76</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>9.553000000000001</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>10.22</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>8.335000000000001</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>7.74</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>5.858</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>5.186</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>10.295</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>10.432</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>5.902</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>9.172000000000001</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>8.271000000000001</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>8.503</v>
       </c>
     </row>
     <row r="68">
@@ -4453,46 +4457,46 @@
         <v>27.674</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>30.001</v>
+        <v>44.528</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>30.093</v>
+        <v>45.853</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>27.674</v>
+        <v>37.227</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>26.437</v>
+        <v>36.657</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>28.906</v>
+        <v>37.241</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>9.428000000000001</v>
+        <v>17.168</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>6.393</v>
+        <v>12.251</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>6.671</v>
+        <v>11.857</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>21.659</v>
+        <v>31.954</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>19.216</v>
+        <v>29.648</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>9.991</v>
+        <v>15.893</v>
       </c>
       <c r="P68" s="3" t="n">
-        <v>13.287</v>
+        <v>22.459</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>11.111</v>
+        <v>19.382</v>
       </c>
       <c r="R68" s="3" t="n">
-        <v>12.278</v>
+        <v>20.781</v>
       </c>
     </row>
     <row r="69">
@@ -4560,13 +4564,13 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>0</v>
+        <v>7.725</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>7.384</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>2.929</v>
       </c>
       <c r="E70" s="3" t="n">
         <v>0</v>
@@ -4618,13 +4622,13 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>8.125999999999999</v>
+        <v>15.851</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>8.707000000000001</v>
+        <v>16.091</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>11.677</v>
+        <v>14.606</v>
       </c>
       <c r="E71" s="3" t="n">
         <v>0</v>
@@ -4853,28 +4857,28 @@
         <v>0</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>11.844</v>
+        <v>4.46</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>18.429</v>
+        <v>15.5</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>12.887</v>
+        <v>0</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>7.146</v>
+        <v>0</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>7.723</v>
+        <v>0</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>9.787000000000001</v>
+        <v>0</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>7.579</v>
+        <v>0</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>32.364</v>
+        <v>24.624</v>
       </c>
       <c r="K75" s="3" t="n">
         <v>0</v>
@@ -4883,22 +4887,22 @@
         <v>0</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>2.559</v>
+        <v>0</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.453</v>
+        <v>0</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>6.262</v>
+        <v>0.36</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>13.233</v>
+        <v>4.061</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>0.396</v>
+        <v>0</v>
       </c>
       <c r="R75" s="3" t="n">
-        <v>1.785</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -5142,13 +5146,13 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>0.2797237748548485</v>
+        <v>0.311898673019734</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>0.3379282861309109</v>
+        <v>0.371366983362165</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.3437639906689601</v>
+        <v>0.3575673319352483</v>
       </c>
       <c r="E80" s="1" t="inlineStr">
         <is>
@@ -6254,10 +6258,10 @@
         <v>-8.981</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>-77.309</v>
+        <v>-81.822</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>-53.689</v>
+        <v>-29.874</v>
       </c>
       <c r="K99" s="3" t="n">
         <v>-30.725</v>
@@ -6812,10 +6816,10 @@
         <v>1.366</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>35.729</v>
+        <v>37.229</v>
       </c>
       <c r="J108" s="3" t="n">
-        <v>0</v>
+        <v>-2.754</v>
       </c>
       <c r="K108" s="3" t="n">
         <v>15.717</v>
@@ -7293,13 +7297,13 @@
         <v>0</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-1.1</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-1.175</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-0.258</v>
       </c>
       <c r="G116" s="3" t="n">
         <v>0</v>
@@ -7524,20 +7528,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P119" s="3" t="n">
+        <v>-32.096</v>
+      </c>
+      <c r="Q119" s="3" t="n">
+        <v>7.386</v>
+      </c>
+      <c r="R119" s="3" t="n">
+        <v>-3.176</v>
       </c>
     </row>
     <row r="120">
@@ -8170,15 +8168,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L129" s="3" t="n">
+        <v>-4.976</v>
+      </c>
+      <c r="M129" s="3" t="n">
+        <v>43.359</v>
       </c>
       <c r="N129" s="1" t="inlineStr">
         <is>
@@ -8525,22 +8519,22 @@
         <v>37.654</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>29.566</v>
+        <v>31.092</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>35.768</v>
+        <v>35.381</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>18.032</v>
+        <v>18.007</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>35.936</v>
+        <v>35.56</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>23.868</v>
+        <v>23.363</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>9.804</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="J135" s="1" t="inlineStr">
         <is>
@@ -8552,15 +8546,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L135" s="3" t="n">
+        <v>-11.412</v>
+      </c>
+      <c r="M135" s="3" t="n">
+        <v>5.491</v>
       </c>
       <c r="N135" s="1" t="inlineStr">
         <is>
@@ -8572,20 +8562,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P135" s="3" t="n">
+        <v>23.616</v>
+      </c>
+      <c r="Q135" s="3" t="n">
+        <v>84.069</v>
+      </c>
+      <c r="R135" s="3" t="n">
+        <v>30.912</v>
       </c>
     </row>
   </sheetData>
@@ -21493,7 +21477,11 @@
           <t>Intangible assets and goodwill, net 11 37,374</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>GoodwillAndOtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -25687,7 +25675,11 @@
           <t>Current portion of capital lease obligations (note 10)</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -28220,7 +28212,11 @@
           <t>Current portion of capital lease obligations (note 11)</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E203" s="5" t="n">
         <v>7.725</v>
       </c>
@@ -30806,7 +30802,11 @@
           <t>Net cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E229" t="inlineStr">
         <is>
           <t>-</t>
@@ -33922,7 +33922,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -34926,7 +34930,11 @@
           <t>Net cash generated from (used in) operating activities</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr"/>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E271" t="inlineStr">
         <is>
           <t>-</t>
@@ -36304,11 +36312,7 @@
           <t>Net income (loss) from continuing operations</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+      <c r="D285" t="inlineStr"/>
       <c r="E285" t="inlineStr">
         <is>
           <t>-</t>
@@ -39500,7 +39504,11 @@
           <t>Net loss from continued operations</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
           <t>-</t>
@@ -42379,7 +42387,11 @@
           <t>(Reversal of) asset impairment charges 10,11</t>
         </is>
       </c>
-      <c r="D346" t="inlineStr"/>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E346" t="inlineStr">
         <is>
           <t>-</t>
@@ -48335,7 +48347,11 @@
           <t>Purchase of intangible assets 10</t>
         </is>
       </c>
-      <c r="D406" t="inlineStr"/>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E406" t="inlineStr">
         <is>
           <t>-</t>
@@ -50028,7 +50044,11 @@
           <t>Purchase of intangible assets 11</t>
         </is>
       </c>
-      <c r="D423" t="inlineStr"/>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E423" t="inlineStr">
         <is>
           <t>-</t>
@@ -51026,7 +51046,11 @@
           <t>Future income tax</t>
         </is>
       </c>
-      <c r="D433" t="inlineStr"/>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E433" t="inlineStr">
         <is>
           <t>-</t>
@@ -53531,7 +53555,11 @@
           <t>Future income tax</t>
         </is>
       </c>
-      <c r="D458" t="inlineStr"/>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E458" s="5" t="n">
         <v>-1.175</v>
       </c>
@@ -66499,7 +66527,11 @@
           <t>Net loss from continued operations</t>
         </is>
       </c>
-      <c r="D588" t="inlineStr"/>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E588" t="inlineStr">
         <is>
           <t>-</t>
@@ -68778,7 +68810,11 @@
           <t>Net loss from continued operations</t>
         </is>
       </c>
-      <c r="D611" t="inlineStr"/>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E611" t="inlineStr">
         <is>
           <t>-</t>
